--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N107_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N107_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.4464487765215</v>
+        <v>2.510047926184743</v>
       </c>
       <c r="D2" t="n">
-        <v>14.81329131277538</v>
+        <v>2.407159838325999</v>
       </c>
       <c r="E2" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F2" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.68198653192581</v>
+        <v>2.385822811437945</v>
       </c>
       <c r="D3" t="n">
-        <v>14.44103872708422</v>
+        <v>2.346668793151185</v>
       </c>
       <c r="E3" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F3" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.34819046106475</v>
+        <v>6.231580949923021</v>
       </c>
       <c r="D4" t="n">
-        <v>37.77323331504336</v>
+        <v>6.138150413694546</v>
       </c>
       <c r="E4" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F4" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.14547585294523</v>
+        <v>7.1736398261036</v>
       </c>
       <c r="D5" t="n">
-        <v>42.94471747524165</v>
+        <v>6.978516589726769</v>
       </c>
       <c r="E5" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F5" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.70360704891619</v>
+        <v>5.639336145448882</v>
       </c>
       <c r="D6" t="n">
-        <v>33.87544061884967</v>
+        <v>5.504759100563072</v>
       </c>
       <c r="E6" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F6" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.98063101487644</v>
+        <v>6.009352539917423</v>
       </c>
       <c r="D7" t="n">
-        <v>36.44485875356466</v>
+        <v>5.922289547454257</v>
       </c>
       <c r="E7" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F7" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.86423714956103</v>
+        <v>3.065438536803667</v>
       </c>
       <c r="D8" t="n">
-        <v>18.13082399266775</v>
+        <v>2.946258898808509</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F8" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.18908098090247</v>
+        <v>8.480725659396652</v>
       </c>
       <c r="D9" t="n">
-        <v>17.67374072207441</v>
+        <v>2.871982867337091</v>
       </c>
       <c r="E9" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F9" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.02559744171869</v>
+        <v>6.991659584279287</v>
       </c>
       <c r="D10" t="n">
-        <v>43.32955557049124</v>
+        <v>7.041052780204827</v>
       </c>
       <c r="E10" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F10" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.58225903909043</v>
+        <v>4.969617093852195</v>
       </c>
       <c r="D11" t="n">
-        <v>8.732124598286489</v>
+        <v>1.418970247221555</v>
       </c>
       <c r="E11" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F11" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.34838675275603</v>
+        <v>7.369112847322856</v>
       </c>
       <c r="D12" t="n">
-        <v>31.18092365533773</v>
+        <v>5.066900093992381</v>
       </c>
       <c r="E12" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F12" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.1938293926714</v>
+        <v>4.418997276309102</v>
       </c>
       <c r="D13" t="n">
-        <v>16.76305461424021</v>
+        <v>2.723996374814035</v>
       </c>
       <c r="E13" t="n">
-        <v>11.80858606698172</v>
+        <v>1.918895235884529</v>
       </c>
       <c r="F13" t="n">
-        <v>11.88874142279</v>
+        <v>1.931920481203375</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
